--- a/unified_template.xlsx
+++ b/unified_template.xlsx
@@ -501,17 +501,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Расход Q, м³/с (пост 10001)</t>
+          <t>Пост 10001</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Расход Q, м³/с (пост 10002)</t>
+          <t>Пост 10002</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Расход Q, м³/с (пост 10003)</t>
+          <t>Пост 10003</t>
         </is>
       </c>
     </row>

--- a/unified_template.xlsx
+++ b/unified_template.xlsx
@@ -3338,348 +3338,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Работа 4 — Максимальный сток (ряды максимумов)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Год | Q_max (м³/с) | Период осреднения: 1 сутки | 5 суток | 7 суток</t>
+          <t>Работа 4 — Максимальный сток (годовые максимумы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Q_max, м³/с</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Год</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Q_max, м³/с</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Q_5сут, м³/с</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Q_7сут, м³/с</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
+      <c r="A4" s="4" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>349.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>591.4</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>397.1</v>
+        <v>748.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>748.8</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>353.8</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>290.2</v>
+        <v>567.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>567.4</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>402.3</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>622.6</v>
+        <v>390.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>390.3</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>431.5</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>648.9</v>
+        <v>317.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>317.7</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>651.2</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>339</v>
+        <v>798.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>798.7</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>445.4</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>392.5</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>416.3</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>529</v>
+        <v>653.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>653.1</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>288.6</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>230.7</v>
+        <v>442.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>442.9</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>613.9</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>629.5</v>
+        <v>325.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>325.7</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>489.5</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>563.2</v>
+        <v>852.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>852.4</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>334.7</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>579.6</v>
+        <v>528.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>528.4</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>732.6</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>357.1</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>376.5</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>749.5</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>258.5</v>
+        <v>891.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>891.7</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>490.9</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>495.3</v>
+        <v>602.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>602.9</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>610.2</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>488.1</v>
+        <v>500.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>500.7</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>384.1</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>628</v>
+        <v>457.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>457.6</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>744.7</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>483.5</v>
+        <v>794.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>794.7</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>261.5</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>396.1</v>
+        <v>434.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>434.4</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>580.6</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>637.2</v>
+        <v>429.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>429.4</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>467.4</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>410.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B25" s="4" t="n">
         <v>802.6</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>710.7</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>564</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/unified_template.xlsx
+++ b/unified_template.xlsx
@@ -12,13 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа8" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа9" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГТС" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КриваяQH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Работа10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГТС" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1356,48 +1357,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Работа 9 — Гидротехнические расчёты (параметры)</t>
+          <t>Работа 8 — Кривая обеспеченности продолжительности (FDC)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Расход паводка Q, м³/с:</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>500</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Расход Q, м³/с</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ширина B, м:</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>45</v>
+      <c r="A4" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>244.3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Уклон I, м/м (или ‰):</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.002</v>
+      <c r="A5" s="4" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>249.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>180.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>174.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>155.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>170.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>136.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>217.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>141.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>134.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>276.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>141.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>148.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>182.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>249.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>165.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>201.1</v>
       </c>
     </row>
   </sheetData>
@@ -1414,251 +1633,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Работа 10 — Экология и базовый сток</t>
+          <t>Работа 9 — Гидротехнические расчёты (параметры)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Год</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Базовый сток, м³/с</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Qэкологический, м³/с</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Расход паводка Q, м³/с:</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>98.2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ширина B, м:</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>99.09999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>93.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>74.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>62.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>47.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>1991</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>51.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>1992</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>51.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>1993</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>27.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>1994</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1995</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>41.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>43.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>38.3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Уклон I, м/м (или ‰):</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.002</v>
       </c>
     </row>
   </sheetData>
@@ -1670,6 +1686,267 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Работа 10 — Экология и базовый сток</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Базовый сток, м³/с</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Qэкологический, м³/с</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>99.09999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3547,359 +3824,191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Работа 5 — Ледовые явления</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Год | Дата ледостава | Дата вскрытия</t>
+          <t>Работа 4 — Кривая расходов Q=f(H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>H, м</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Q, м³/с</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Год</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Дата ледостава</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Дата вскрытия</t>
-        </is>
+      <c r="A4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>1970-11-20</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>1971-04-10</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>12.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>1971-11-20</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>1972-04-10</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>21.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>1972-11-20</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>1973-04-10</t>
-        </is>
+        <v>1.25</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>30.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1973-11-20</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>1974-04-10</t>
-        </is>
+        <v>1.5</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>37.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>1974-11-20</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>1975-04-10</t>
-        </is>
+        <v>1.75</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>45.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>1975-11-20</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>1976-04-10</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>1976-11-20</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>1977-04-10</t>
-        </is>
+        <v>2.25</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>1977-11-20</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>1978-04-10</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>1978-11-20</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>1979-04-10</t>
-        </is>
+        <v>2.75</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>1979-11-20</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>1980-04-10</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>103.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>1980-11-20</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>1981-04-10</t>
-        </is>
+        <v>3.25</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>113.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>1981-11-20</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>1982-04-10</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>126.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>1982-11-20</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>1983-04-10</t>
-        </is>
+        <v>3.75</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>143.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>1983-11-20</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>1984-04-10</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>164.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>1984-11-20</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>1985-04-10</t>
-        </is>
+        <v>4.25</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>179.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>1985-11-20</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>1986-04-10</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>188.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>1986-11-20</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>1987-04-10</t>
-        </is>
+        <v>4.75</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>211.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>1987-11-20</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>1988-04-10</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>221.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>1988-11-20</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>1989-04-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>1989-11-20</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>1990-04-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>1990-11-20</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>1991-04-10</t>
-        </is>
+        <v>5.25</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>237.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3911,6 +4020,370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Работа 5 — Ледовые явления</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Год | Дата ледостава | Дата вскрытия</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Дата ледостава</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Дата вскрытия</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1970-11-20</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1971-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1971-11-20</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1972-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>1972-11-20</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1973-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>1973-11-20</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>1974-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>1974-11-20</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1975-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>1975-11-20</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1976-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>1976-11-20</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1977-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1977-11-20</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>1978-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1978-11-20</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1979-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>1979-11-20</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1980-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>1980-11-20</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1981-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1981-11-20</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>1982-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>1982-11-20</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>1983-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>1983-11-20</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>1984-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1984-11-20</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1985-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1985-11-20</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>1986-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>1986-11-20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>1987-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1987-11-20</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>1988-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>1988-11-20</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>1989-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>1989-11-20</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1990-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1990-11-20</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>1991-04-10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4231,7 +4704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4309,280 +4782,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Работа 8 — Кривая обеспеченности продолжительности (FDC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Год</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Расход Q, м³/с</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>244.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>249.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>180.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>174.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>155.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>170.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>136.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>217.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>1991</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>141.7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>1992</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>134.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>1993</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>276.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>1994</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>178.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1995</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>141.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>170.3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>148.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>78.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>182.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>83.09999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>172.1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>249.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>102.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>55.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>165.7</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>201.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/unified_template.xlsx
+++ b/unified_template.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,6 +111,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,6 +501,10 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -517,832 +528,833 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1960</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>139.7</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>107.1</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="8" t="n">
         <v>195.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1961</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>132.1</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="8" t="n">
         <v>121.7</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>123.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1962</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>130.7</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>160.6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1963</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>127.3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>98.3</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>122.2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1964</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>180.5</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>200.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1965</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>162.6</v>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n">
         <v>203.4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>144.1</v>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n">
         <v>166.6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1967</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n">
         <v>162.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>148.6</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="8" t="n">
         <v>123.4</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="8" t="n">
         <v>160.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1969</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="8" t="n">
         <v>74.8</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="8" t="n">
         <v>123.7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>102.5</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="8" t="n">
         <v>76.5</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="8" t="n">
         <v>106.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="8" t="n">
         <v>116.8</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="8" t="n">
         <v>174.5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>181</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="8" t="n">
         <v>208.8</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>156.2</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="8" t="n">
         <v>169.8</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>127.7</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="8" t="n">
         <v>111.9</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="8" t="n">
         <v>179.1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>147.5</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="8" t="n">
         <v>135.3</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="8" t="n">
         <v>179.2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>1976</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>128.2</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="8" t="n">
         <v>109.2</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="8" t="n">
         <v>117.1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>1977</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="8" t="n">
         <v>126.6</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="8" t="n">
         <v>148.3</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="8" t="n">
         <v>1978</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="8" t="n">
         <v>152</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="8" t="n">
         <v>126</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="8" t="n">
         <v>164.8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="8" t="n">
         <v>1979</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="8" t="n">
         <v>125.2</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="8" t="n">
         <v>139.1</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="8" t="n">
         <v>156.8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="8" t="n">
         <v>171</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="D28" s="4" t="n"/>
+      <c r="D28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="8" t="n">
         <v>82.3</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="8" t="n">
         <v>123.6</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="8" t="n">
         <v>125.5</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="8" t="n">
         <v>93.8</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="8" t="n">
         <v>151.9</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="8" t="n">
         <v>138.1</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="8" t="n">
         <v>123.1</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="8" t="n">
         <v>171.8</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="8" t="n">
         <v>168.2</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="8" t="n">
         <v>140.3</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="8" t="n">
         <v>175.4</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="8" t="n">
         <v>166.7</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="8" t="n">
         <v>150.2</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="8" t="n">
         <v>186.7</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="8" t="n">
         <v>147.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="8" t="n">
         <v>133.7</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="8" t="n">
         <v>112.8</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="8" t="n">
         <v>143.9</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="8" t="n">
         <v>135.6</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="8" t="n">
         <v>105.1</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="8" t="n">
         <v>182.4</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="8" t="n">
         <v>169.3</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="8" t="n">
         <v>125.7</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="8" t="n">
         <v>200.8</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="8" t="n">
         <v>141.8</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="8" t="n">
         <v>115.2</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="8" t="n">
         <v>144.2</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="8" t="n">
         <v>1991</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="8" t="n">
         <v>137.8</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="8" t="n">
         <v>172.3</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="8" t="n">
         <v>1992</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="8" t="n">
         <v>122.4</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="8" t="n">
         <v>106.6</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="8" t="n">
         <v>172.5</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="8" t="n">
         <v>1993</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="8" t="n">
         <v>166.2</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="8" t="n">
         <v>126.3</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="8" t="n">
         <v>206.6</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="8" t="n">
         <v>1994</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="8" t="n">
         <v>166.5</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="8" t="n">
         <v>143.6</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="8" t="n">
         <v>168.7</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="8" t="n">
         <v>1995</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="8" t="n">
         <v>183.8</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="8" t="n">
         <v>160.9</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="8" t="n">
         <v>204.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="8" t="n">
         <v>1996</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="8" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="8" t="n">
         <v>159.3</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="8" t="n">
         <v>1997</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="8" t="n">
         <v>138</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="8" t="n">
         <v>119.1</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="8" t="n">
         <v>148.1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="8" t="n">
         <v>1998</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="8" t="n">
         <v>143.4</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="8" t="n">
         <v>122.6</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="8" t="n">
         <v>171.6</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="8" t="n">
         <v>1999</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="8" t="n">
         <v>134.2</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="8" t="n">
         <v>100.3</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="8" t="n">
         <v>165.9</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="8" t="n">
         <v>171.3</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="8" t="n">
         <v>149.9</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="8" t="n">
         <v>183.1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="8" t="n">
         <v>2001</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="8" t="n">
         <v>195.2</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="8" t="n">
         <v>172.7</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="8" t="n">
         <v>223.6</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="8" t="n">
         <v>2002</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="8" t="n">
         <v>145.4</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="8" t="n">
         <v>136.6</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="8" t="n">
         <v>118.6</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="8" t="n">
         <v>2003</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="8" t="n">
         <v>128.1</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="8" t="n">
         <v>140.9</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="8" t="n">
         <v>2004</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="8" t="n">
         <v>111.8</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="8" t="n">
         <v>169.8</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="8" t="n">
         <v>2005</v>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n">
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n">
         <v>157.1</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="8" t="n">
         <v>209</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="8" t="n">
         <v>2006</v>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n">
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n">
         <v>127.3</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="8" t="n">
         <v>188.4</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="8" t="n">
         <v>2007</v>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n">
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n">
         <v>119</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="8" t="n">
         <v>131.3</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="8" t="n">
         <v>2008</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="8" t="n">
         <v>149.7</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="8" t="n">
         <v>133.4</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="8" t="n">
         <v>165.5</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="8" t="n">
         <v>2009</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="8" t="n">
         <v>162.3</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="8" t="n">
         <v>184.2</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="8" t="n">
         <v>188.6</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="8" t="n">
         <v>2010</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="8" t="n">
         <v>121.2</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="8" t="n">
         <v>176.3</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="8" t="n">
         <v>2011</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="8" t="n">
         <v>142.4</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="8" t="n">
         <v>134.7</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="8" t="n">
         <v>142.3</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="8" t="n">
         <v>2012</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="8" t="n">
         <v>169.9</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="8" t="n">
         <v>155.8</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="8" t="n">
         <v>212.8</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="8" t="n">
         <v>2013</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="8" t="n">
         <v>162.1</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="8" t="n">
         <v>145.6</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="8" t="n">
         <v>186.5</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="8" t="n">
         <v>2014</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="8" t="n">
         <v>129.7</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="8" t="n">
         <v>165.9</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="8" t="n">
         <v>2015</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="8" t="n">
         <v>171.8</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="8" t="n">
         <v>155.2</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="8" t="n">
         <v>204.5</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="8" t="n">
         <v>2016</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="8" t="n">
         <v>151.3</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="8" t="n">
         <v>119.3</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="8" t="n">
         <v>177</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="8" t="n">
         <v>2017</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="8" t="n">
         <v>162.4</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="8" t="n">
         <v>2018</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="8" t="n">
         <v>151.1</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="8" t="n">
         <v>122.6</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="8" t="n">
         <v>174.8</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="8" t="n">
         <v>2019</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="8" t="n">
         <v>165.3</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="8" t="n">
         <v>141.5</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="8" t="n">
         <v>184.3</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -1367,6 +1379,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1380,246 +1393,247 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>244.3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>249.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>180.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>174.3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>155.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>170.8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>136.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>264</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>217.8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1991</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>141.7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1992</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>134.6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1993</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>276.4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1994</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>178.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1995</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>75.90000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1996</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>141.2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1997</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>170.3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1998</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>148.5</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1999</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>58.6</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>78.2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>2001</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="8" t="n">
         <v>182.8</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="8" t="n">
         <v>2002</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="8" t="n">
         <v>83.09999999999999</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="8" t="n">
         <v>2003</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="8" t="n">
         <v>172.1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="8" t="n">
         <v>2004</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="8" t="n">
         <v>249.3</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="8" t="n">
         <v>2005</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="8" t="n">
         <v>102.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="8" t="n">
         <v>2006</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="8" t="n">
         <v>56.4</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="8" t="n">
         <v>2007</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="8" t="n">
         <v>55.1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="8" t="n">
         <v>2008</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="8" t="n">
         <v>165.7</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="8" t="n">
         <v>2009</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="8" t="n">
         <v>201.1</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1647,13 +1661,14 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Расход паводка Q, м³/с:</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="9" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1663,7 +1678,7 @@
           <t>Ширина B, м:</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="9" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1673,11 +1688,12 @@
           <t>Уклон I, м/м (или ‰):</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>0.002</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1701,6 +1717,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1719,226 +1736,227 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="8" t="n">
         <v>98.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>84.8</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="8" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="8" t="n">
         <v>31.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="8" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>55.4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="8" t="n">
         <v>99.09999999999999</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>93.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>74.2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>33.4</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>27.3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="8" t="n">
         <v>62.3</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>59.4</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>47.7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1991</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>60.1</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="8" t="n">
         <v>51.2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1992</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>43.2</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="8" t="n">
         <v>51.1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1993</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="8" t="n">
         <v>27.7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1994</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="8" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1995</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="8" t="n">
         <v>42.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1996</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="8" t="n">
         <v>56.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1997</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>38.9</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="8" t="n">
         <v>41.6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1998</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>51.2</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="8" t="n">
         <v>43.2</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1999</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="8" t="n">
         <v>38.3</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1966,13 +1984,14 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Высота плотины, м:</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="9" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1982,11 +2001,12 @@
           <t>Объём водохранилища, млн.м³:</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="9" t="n">
         <v>200</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2011,6 +2031,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2024,7 +2045,7 @@
           <t>Название:</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Бирюса, с. Шиткино</t>
         </is>
@@ -2036,10 +2057,11 @@
           <t>Площадь F, км²:</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>31800</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -2053,261 +2075,266 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1944</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>361</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1945</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1946</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>364</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1947</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1948</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1949</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1950</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>287</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1951</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>284</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1952</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>403</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1953</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>274</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1954</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>306</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1955</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>395</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1956</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>243</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1957</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>291</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1958</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1959</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>264</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>1960</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>276</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>1961</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="8" t="n">
         <v>288</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="8" t="n">
         <v>1962</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="8" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="8" t="n">
         <v>1963</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="8" t="n">
         <v>266</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="8" t="n">
         <v>1964</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="8" t="n">
         <v>243</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="8" t="n">
         <v>1965</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="8" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="8" t="n">
         <v>376</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="8" t="n">
         <v>1967</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="8" t="n">
         <v>308</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="8" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="8" t="n">
         <v>1969</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="8" t="n">
         <v>226</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="8" t="n">
         <v>226</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="8" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="8" t="n">
         <v>307</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="8" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="8" t="n">
         <v>203</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="8" t="n">
         <v>290</v>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -2321,7 +2348,7 @@
           <t>Название:</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Бирюса, р.п. Суетиха</t>
         </is>
@@ -2333,10 +2360,11 @@
           <t>Площадь F, км²:</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="9" t="n">
         <v>24700</v>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -2350,326 +2378,327 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="8" t="n">
         <v>1936</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="8" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="8" t="n">
         <v>1937</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="8" t="n">
         <v>280</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="8" t="n">
         <v>1938</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="8" t="n">
         <v>276</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="8" t="n">
         <v>1939</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="8" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="8" t="n">
         <v>1940</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="8" t="n">
         <v>252</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="8" t="n">
         <v>1941</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="8" t="n">
         <v>339</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="8" t="n">
         <v>1942</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="8" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="8" t="n">
         <v>1943</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="8" t="n">
         <v>159</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="8" t="n">
         <v>1944</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="8" t="n">
         <v>329</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="8" t="n">
         <v>1945</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="8" t="n">
         <v>177</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="8" t="n">
         <v>1946</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="8" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="8" t="n">
         <v>1947</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="8" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="8" t="n">
         <v>1948</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="8" t="n">
         <v>203</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="8" t="n">
         <v>1949</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="8" t="n">
         <v>221</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="8" t="n">
         <v>1950</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="8" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="8" t="n">
         <v>1951</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="8" t="n">
         <v>249</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="8" t="n">
         <v>1952</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="8" t="n">
         <v>368</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="8" t="n">
         <v>1953</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="8" t="n">
         <v>243</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="8" t="n">
         <v>1954</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="8" t="n">
         <v>283</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="8" t="n">
         <v>1955</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="8" t="n">
         <v>367</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="8" t="n">
         <v>1956</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="8" t="n">
         <v>218</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="8" t="n">
         <v>1957</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="8" t="n">
         <v>256</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="8" t="n">
         <v>1958</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="8" t="n">
         <v>223</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="8" t="n">
         <v>1959</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="8" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="8" t="n">
         <v>1960</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="8" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="8" t="n">
         <v>1961</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="8" t="n">
         <v>269</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="8" t="n">
         <v>1962</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="8" t="n">
         <v>252</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="8" t="n">
         <v>1963</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="8" t="n">
         <v>244</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="8" t="n">
         <v>1964</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="8" t="n">
         <v>215</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="8" t="n">
         <v>1965</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="8" t="n">
         <v>297</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="8" t="n">
         <v>341</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="8" t="n">
         <v>1967</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="8" t="n">
         <v>280</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="8" t="n">
         <v>203</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="8" t="n">
         <v>1969</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="8" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="8" t="n">
         <v>369</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="8" t="n">
         <v>252</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="8" t="n">
         <v>278</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="8" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="8" t="n">
         <v>181</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="8" t="n">
         <v>264</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2700,6 +2729,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2768,457 +2798,458 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1965</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>57.6</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="8" t="n">
         <v>59.6</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="8" t="n">
         <v>38.5</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="8" t="n">
         <v>38.6</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="8" t="n">
         <v>36.4</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="8" t="n">
         <v>43.4</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="8" t="n">
         <v>25.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>7.6</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="8" t="n">
         <v>57.1</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="8" t="n">
         <v>42.7</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="8" t="n">
         <v>55.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1967</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="8" t="n">
         <v>49.9</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="8" t="n">
         <v>37.9</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="8" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="8" t="n">
         <v>47.8</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="8" t="n">
         <v>58.6</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="8" t="n">
         <v>50.2</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="8" t="n">
         <v>47.6</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="8" t="n">
         <v>50.1</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="8" t="n">
         <v>34.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1969</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>37.4</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="8" t="n">
         <v>42.8</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="8" t="n">
         <v>18.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="8" t="n">
         <v>57.6</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="8" t="n">
         <v>50.7</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="8" t="n">
         <v>44.1</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="8" t="n">
         <v>55.7</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="8" t="n">
         <v>53.2</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="8" t="n">
         <v>9.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>51.1</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>57.1</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="8" t="n">
         <v>34.9</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="8" t="n">
         <v>54.5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="8" t="n">
         <v>7.8</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="8" t="n">
         <v>49.3</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="8" t="n">
         <v>52.6</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="8" t="n">
         <v>31.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="8" t="n">
         <v>36.4</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="8" t="n">
         <v>34.6</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="8" t="n">
         <v>42.3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="8" t="n">
         <v>39.6</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="8" t="n">
         <v>39.4</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="8" t="n">
         <v>43.7</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="8" t="n">
         <v>41.1</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="M13" s="8" t="n">
         <v>28.4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>59.3</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="8" t="n">
         <v>39.1</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="8" t="n">
         <v>36.5</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="8" t="n">
         <v>46.9</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="8" t="n">
         <v>7.1</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" s="8" t="n">
         <v>53.5</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="8" t="n">
         <v>14.6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>34.9</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="8" t="n">
         <v>46.9</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="8" t="n">
         <v>35.9</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="8" t="n">
         <v>46.5</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="8" t="n">
         <v>47.6</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="8" t="n">
         <v>59.2</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="8" t="n">
         <v>29.9</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -3243,6 +3274,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3266,13 +3298,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>2.91</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="8" t="n">
         <v>5.86</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3282,13 +3314,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>2.91</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="8" t="n">
         <v>12.33</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3298,13 +3330,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>5.79</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="8" t="n">
         <v>4.48</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3314,13 +3346,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>7.83</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="8" t="n">
         <v>6.78</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3330,13 +3362,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>2.54</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>13.12</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3346,13 +3378,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>6.99</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="8" t="n">
         <v>8.220000000000001</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3362,13 +3394,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1976</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>4.36</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>6.65</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3378,13 +3410,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1977</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>2.77</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>6.89</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3394,13 +3426,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1978</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>3.1</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>13.68</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3410,13 +3442,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1979</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>7.07</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="8" t="n">
         <v>10.86</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -3426,13 +3458,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>2.85</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>11.07</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3442,13 +3474,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>6.55</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="8" t="n">
         <v>6.13</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3458,13 +3490,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>5.51</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="8" t="n">
         <v>6.76</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3474,13 +3506,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>1.94</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="8" t="n">
         <v>8.42</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3490,13 +3522,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>3.96</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="8" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3506,13 +3538,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>4.43</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="8" t="n">
         <v>4.22</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3522,13 +3554,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>7.92</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="8" t="n">
         <v>14.39</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -3538,13 +3570,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>7.18</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="8" t="n">
         <v>8.69</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -3554,13 +3586,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>4.71</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="8" t="n">
         <v>13.17</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -3570,13 +3602,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>4.13</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="8" t="n">
         <v>6.05</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3586,13 +3618,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>7.36</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="8" t="n">
         <v>7.87</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3602,6 +3634,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3625,6 +3658,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3643,174 +3677,175 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>349.9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>748.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>567.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>390.3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>317.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>798.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1976</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>473.3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1977</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>653.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1978</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>442.9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1979</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>325.7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>852.4</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>528.4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>376.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>891.7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>602.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>500.7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>457.6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>794.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>434.4</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>429.4</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="8" t="n">
         <v>802.6</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -3834,6 +3869,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3847,166 +3883,167 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>12.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>21.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1.25</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>30.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>37.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1.75</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>45.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>55.1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>2.25</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>71.59999999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>2.75</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>93.59999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>103.4</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>3.25</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>113.6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>3.5</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>126.8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>3.75</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>143.9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>164.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>4.25</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>179.6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>4.5</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>188.3</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>4.75</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>211.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>221.8</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>5.25</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>237.5</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -4037,6 +4074,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4055,321 +4093,322 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1970</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>1970-11-20</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>1971-04-10</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1971</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>1971-11-20</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>1972-04-10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1972</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>1972-11-20</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>1973-04-10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1973</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>1973-11-20</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>1974-04-10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1974</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>1974-11-20</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>1975-04-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1975</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>1975-11-20</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>1976-04-10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1976</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>1976-11-20</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>1977-04-10</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1977</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1977-11-20</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>1978-04-10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1978</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>1978-11-20</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>1979-04-10</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1979</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>1979-11-20</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>1980-04-10</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>1980-11-20</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>1981-04-10</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>1981-11-20</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>1982-04-10</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>1982-11-20</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>1983-04-10</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>1983-11-20</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>1984-04-10</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>1984-11-20</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>1985-04-10</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>1985-11-20</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>1986-04-10</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>1986-11-20</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>1987-04-10</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>1987-11-20</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>1988-04-10</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>1988-11-20</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>1989-04-10</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>1989-11-20</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>1990-04-10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>1990-11-20</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>1991-04-10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -4394,6 +4433,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4417,286 +4457,287 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>1980</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="8" t="n">
         <v>507.5</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="8" t="n">
         <v>195.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="8" t="n">
         <v>256.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1981</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="8" t="n">
         <v>650.8</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="8" t="n">
         <v>229</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="8" t="n">
         <v>268.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="8" t="n">
         <v>638.9</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="8" t="n">
         <v>252.8</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="8" t="n">
         <v>391.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>1983</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="8" t="n">
         <v>552.8</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="8" t="n">
         <v>215.6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="8" t="n">
         <v>352.6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>1984</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>586.2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="8" t="n">
         <v>208.7</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="8" t="n">
         <v>295.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>1985</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="8" t="n">
         <v>591.4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="8" t="n">
         <v>274.8</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="8" t="n">
         <v>398.8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="8" t="n">
         <v>611.1</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="8" t="n">
         <v>273.9</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>1987</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="8" t="n">
         <v>677.1</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="8" t="n">
         <v>184.9</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="8" t="n">
         <v>331.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>1988</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="8" t="n">
         <v>555.8</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="8" t="n">
         <v>186.7</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>386.6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>1989</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="8" t="n">
         <v>581.8</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="8" t="n">
         <v>178.7</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="8" t="n">
         <v>367.8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>1990</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="8" t="n">
         <v>522.8</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="8" t="n">
         <v>291.5</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="8" t="n">
         <v>304.1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>1991</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="8" t="n">
         <v>534</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="8" t="n">
         <v>156.4</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="8" t="n">
         <v>315.7</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>1992</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="8" t="n">
         <v>598.7</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="8" t="n">
         <v>190.5</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="8" t="n">
         <v>279.8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>1993</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="8" t="n">
         <v>518.3</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="8" t="n">
         <v>265.4</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="8" t="n">
         <v>283.4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>1994</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="8" t="n">
         <v>686.1</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="8" t="n">
         <v>247.9</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="8" t="n">
         <v>280.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>1995</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="8" t="n">
         <v>605.3</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="8" t="n">
         <v>229.6</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="8" t="n">
         <v>378.2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>1996</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="8" t="n">
         <v>540.6</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="8" t="n">
         <v>189.7</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="8" t="n">
         <v>353.1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>1997</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="8" t="n">
         <v>526.5</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="8" t="n">
         <v>261.8</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="8" t="n">
         <v>379.8</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>1998</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="8" t="n">
         <v>681.3</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="8" t="n">
         <v>198.1</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="8" t="n">
         <v>287.3</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>1999</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="8" t="n">
         <v>537.8</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="8" t="n">
         <v>213.5</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="8" t="n">
         <v>315.1</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -4724,13 +4765,14 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Площадь бассейна F, км²:</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="9" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4740,7 +4782,7 @@
           <t>Климатическая зона (zone_1 ... zone_7):</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>zone_3</t>
         </is>
@@ -4752,7 +4794,7 @@
           <t>Обеспеченность T, лет:</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4762,7 +4804,7 @@
           <t>Время концентрации t, мин:</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="9" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4772,11 +4814,12 @@
           <t>Коэфф. стока α:</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="9" t="n">
         <v>0.7</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>

--- a/unified_template.xlsx
+++ b/unified_template.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,26 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -488,40 +508,66 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Данные гидрологического поста для статистической обработки</t>
         </is>
       </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Заполни данные в жёлтых ячейках или оставь как есть</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Пост 10001</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Пост 10002</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Пост 10003</t>
         </is>
@@ -1354,7 +1400,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -1373,20 +1418,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 8 — Кривая обеспеченности продолжительности (FDC)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Расход Q, м³/с</t>
         </is>
@@ -1633,7 +1682,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1655,15 +1703,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 9 — Гидротехнические расчёты (параметры)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Расход паводка Q, м³/с:</t>
         </is>
@@ -1673,7 +1725,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Ширина B, м:</t>
         </is>
@@ -1683,7 +1735,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Уклон I, м/м (или ‰):</t>
         </is>
@@ -1693,7 +1745,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1711,25 +1762,31 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 10 — Экология и базовый сток</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Базовый сток, м³/с</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Qэкологический, м³/с</t>
         </is>
@@ -1956,7 +2013,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1978,15 +2034,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Параметры ГТС для классификации</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Высота плотины, м:</t>
         </is>
@@ -1996,7 +2056,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Объём водохранилища, млн.м³:</t>
         </is>
@@ -2006,7 +2066,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2025,22 +2084,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 1 — Норма годового стока</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>РАСЧЁТНАЯ РЕКА</t>
         </is>
       </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Название:</t>
         </is>
@@ -2050,9 +2123,12 @@
           <t>Бирюса, с. Шиткино</t>
         </is>
       </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Площадь F, км²:</t>
         </is>
@@ -2060,19 +2136,31 @@
       <c r="B5" s="9" t="n">
         <v>31800</v>
       </c>
-    </row>
-    <row r="6"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Q, м³/с</t>
         </is>
       </c>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -2081,6 +2169,9 @@
       <c r="B8" s="8" t="n">
         <v>361</v>
       </c>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -2089,6 +2180,9 @@
       <c r="B9" s="8" t="n">
         <v>210</v>
       </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2097,6 +2191,9 @@
       <c r="B10" s="8" t="n">
         <v>364</v>
       </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -2105,6 +2202,9 @@
       <c r="B11" s="8" t="n">
         <v>250</v>
       </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -2113,6 +2213,9 @@
       <c r="B12" s="8" t="n">
         <v>225</v>
       </c>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -2121,6 +2224,9 @@
       <c r="B13" s="8" t="n">
         <v>241</v>
       </c>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -2129,6 +2235,9 @@
       <c r="B14" s="8" t="n">
         <v>287</v>
       </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -2137,6 +2246,9 @@
       <c r="B15" s="8" t="n">
         <v>284</v>
       </c>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -2145,6 +2257,9 @@
       <c r="B16" s="8" t="n">
         <v>403</v>
       </c>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -2153,6 +2268,9 @@
       <c r="B17" s="8" t="n">
         <v>274</v>
       </c>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -2161,6 +2279,9 @@
       <c r="B18" s="8" t="n">
         <v>306</v>
       </c>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -2169,6 +2290,9 @@
       <c r="B19" s="8" t="n">
         <v>395</v>
       </c>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -2177,6 +2301,9 @@
       <c r="B20" s="8" t="n">
         <v>243</v>
       </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -2185,6 +2312,9 @@
       <c r="B21" s="8" t="n">
         <v>291</v>
       </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -2193,6 +2323,9 @@
       <c r="B22" s="8" t="n">
         <v>253</v>
       </c>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -2201,6 +2334,9 @@
       <c r="B23" s="8" t="n">
         <v>264</v>
       </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -2209,6 +2345,9 @@
       <c r="B24" s="8" t="n">
         <v>276</v>
       </c>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -2217,6 +2356,9 @@
       <c r="B25" s="8" t="n">
         <v>288</v>
       </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
@@ -2225,6 +2367,9 @@
       <c r="B26" s="8" t="n">
         <v>268</v>
       </c>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -2233,6 +2378,9 @@
       <c r="B27" s="8" t="n">
         <v>266</v>
       </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -2241,6 +2389,9 @@
       <c r="B28" s="8" t="n">
         <v>243</v>
       </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -2249,6 +2400,9 @@
       <c r="B29" s="8" t="n">
         <v>318</v>
       </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
@@ -2257,6 +2411,9 @@
       <c r="B30" s="8" t="n">
         <v>376</v>
       </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -2265,6 +2422,9 @@
       <c r="B31" s="8" t="n">
         <v>308</v>
       </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -2273,6 +2433,9 @@
       <c r="B32" s="8" t="n">
         <v>310</v>
       </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
@@ -2281,6 +2444,9 @@
       <c r="B33" s="8" t="n">
         <v>226</v>
       </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -2289,6 +2455,9 @@
       <c r="B34" s="8" t="n">
         <v>226</v>
       </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -2297,6 +2466,9 @@
       <c r="B35" s="8" t="n">
         <v>260</v>
       </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -2305,6 +2477,9 @@
       <c r="B36" s="8" t="n">
         <v>307</v>
       </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -2313,6 +2488,9 @@
       <c r="B37" s="8" t="n">
         <v>372</v>
       </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -2321,6 +2499,9 @@
       <c r="B38" s="8" t="n">
         <v>203</v>
       </c>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
@@ -2329,21 +2510,58 @@
       <c r="B39" s="8" t="n">
         <v>290</v>
       </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>РЕКА-АНАЛОГ</t>
         </is>
       </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Название:</t>
         </is>
@@ -2353,9 +2571,12 @@
           <t>Бирюса, р.п. Суетиха</t>
         </is>
       </c>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Площадь F, км²:</t>
         </is>
@@ -2363,19 +2584,31 @@
       <c r="B47" s="9" t="n">
         <v>24700</v>
       </c>
-    </row>
-    <row r="48"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Q, м³/с</t>
         </is>
       </c>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -2384,6 +2617,9 @@
       <c r="B50" s="8" t="n">
         <v>335</v>
       </c>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
@@ -2392,6 +2628,9 @@
       <c r="B51" s="8" t="n">
         <v>280</v>
       </c>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
@@ -2400,6 +2639,9 @@
       <c r="B52" s="8" t="n">
         <v>276</v>
       </c>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
@@ -2408,6 +2650,9 @@
       <c r="B53" s="8" t="n">
         <v>292</v>
       </c>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
@@ -2416,6 +2661,9 @@
       <c r="B54" s="8" t="n">
         <v>252</v>
       </c>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
@@ -2424,6 +2672,9 @@
       <c r="B55" s="8" t="n">
         <v>339</v>
       </c>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
@@ -2432,6 +2683,9 @@
       <c r="B56" s="8" t="n">
         <v>200</v>
       </c>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
@@ -2440,6 +2694,9 @@
       <c r="B57" s="8" t="n">
         <v>159</v>
       </c>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -2448,6 +2705,9 @@
       <c r="B58" s="8" t="n">
         <v>329</v>
       </c>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -2456,6 +2716,9 @@
       <c r="B59" s="8" t="n">
         <v>177</v>
       </c>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -2464,6 +2727,9 @@
       <c r="B60" s="8" t="n">
         <v>320</v>
       </c>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
@@ -2472,6 +2738,9 @@
       <c r="B61" s="8" t="n">
         <v>229</v>
       </c>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
@@ -2480,6 +2749,9 @@
       <c r="B62" s="8" t="n">
         <v>203</v>
       </c>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
@@ -2488,6 +2760,9 @@
       <c r="B63" s="8" t="n">
         <v>221</v>
       </c>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
@@ -2496,6 +2771,9 @@
       <c r="B64" s="8" t="n">
         <v>262</v>
       </c>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -2504,6 +2782,9 @@
       <c r="B65" s="8" t="n">
         <v>249</v>
       </c>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
@@ -2512,6 +2793,9 @@
       <c r="B66" s="8" t="n">
         <v>368</v>
       </c>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -2520,6 +2804,9 @@
       <c r="B67" s="8" t="n">
         <v>243</v>
       </c>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -2528,6 +2815,9 @@
       <c r="B68" s="8" t="n">
         <v>283</v>
       </c>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
@@ -2536,6 +2826,9 @@
       <c r="B69" s="8" t="n">
         <v>367</v>
       </c>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
@@ -2544,6 +2837,9 @@
       <c r="B70" s="8" t="n">
         <v>218</v>
       </c>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
@@ -2552,6 +2848,9 @@
       <c r="B71" s="8" t="n">
         <v>256</v>
       </c>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="11" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -2560,6 +2859,9 @@
       <c r="B72" s="8" t="n">
         <v>223</v>
       </c>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -2568,6 +2870,9 @@
       <c r="B73" s="8" t="n">
         <v>250</v>
       </c>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="11" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
@@ -2576,6 +2881,9 @@
       <c r="B74" s="8" t="n">
         <v>260</v>
       </c>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
@@ -2584,6 +2892,9 @@
       <c r="B75" s="8" t="n">
         <v>269</v>
       </c>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
@@ -2592,6 +2903,9 @@
       <c r="B76" s="8" t="n">
         <v>252</v>
       </c>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
@@ -2600,6 +2914,9 @@
       <c r="B77" s="8" t="n">
         <v>244</v>
       </c>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -2608,6 +2925,9 @@
       <c r="B78" s="8" t="n">
         <v>215</v>
       </c>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
@@ -2616,6 +2936,9 @@
       <c r="B79" s="8" t="n">
         <v>297</v>
       </c>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -2624,6 +2947,9 @@
       <c r="B80" s="8" t="n">
         <v>341</v>
       </c>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -2632,6 +2958,9 @@
       <c r="B81" s="8" t="n">
         <v>280</v>
       </c>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
@@ -2640,6 +2969,9 @@
       <c r="B82" s="8" t="n">
         <v>203</v>
       </c>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
@@ -2648,6 +2980,9 @@
       <c r="B83" s="8" t="n">
         <v>250</v>
       </c>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
@@ -2656,6 +2991,9 @@
       <c r="B84" s="8" t="n">
         <v>369</v>
       </c>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
@@ -2664,6 +3002,9 @@
       <c r="B85" s="8" t="n">
         <v>252</v>
       </c>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
@@ -2672,6 +3013,9 @@
       <c r="B86" s="8" t="n">
         <v>278</v>
       </c>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
@@ -2680,6 +3024,9 @@
       <c r="B87" s="8" t="n">
         <v>323</v>
       </c>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="11" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
@@ -2688,6 +3035,9 @@
       <c r="B88" s="8" t="n">
         <v>181</v>
       </c>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
@@ -2696,9 +3046,11 @@
       <c r="B89" s="8" t="n">
         <v>264</v>
       </c>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2716,82 +3068,120 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 2 — Внутригодовое распределение (помесячные расходы)</t>
         </is>
       </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Год | I | II | III | IV | V | VI | VII | VIII | IX | X | XI | XII</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
@@ -3249,7 +3639,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -3268,30 +3657,38 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 3 — Минимальный сток (30-суточные минимумы)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Зимний минимум</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Летний минимум</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -3307,7 +3704,7 @@
       <c r="C4" s="8" t="n">
         <v>5.86</v>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3323,7 +3720,7 @@
       <c r="C5" s="8" t="n">
         <v>12.33</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3339,7 +3736,7 @@
       <c r="C6" s="8" t="n">
         <v>4.48</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3355,7 +3752,7 @@
       <c r="C7" s="8" t="n">
         <v>6.78</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3371,7 +3768,7 @@
       <c r="C8" s="8" t="n">
         <v>13.12</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3387,7 +3784,7 @@
       <c r="C9" s="8" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3403,7 +3800,7 @@
       <c r="C10" s="8" t="n">
         <v>6.65</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3419,7 +3816,7 @@
       <c r="C11" s="8" t="n">
         <v>6.89</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3435,7 +3832,7 @@
       <c r="C12" s="8" t="n">
         <v>13.68</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3451,7 +3848,7 @@
       <c r="C13" s="8" t="n">
         <v>10.86</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3467,7 +3864,7 @@
       <c r="C14" s="8" t="n">
         <v>11.07</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3483,7 +3880,7 @@
       <c r="C15" s="8" t="n">
         <v>6.13</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3499,7 +3896,7 @@
       <c r="C16" s="8" t="n">
         <v>6.76</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3515,7 +3912,7 @@
       <c r="C17" s="8" t="n">
         <v>8.42</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3531,7 +3928,7 @@
       <c r="C18" s="8" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3547,7 +3944,7 @@
       <c r="C19" s="8" t="n">
         <v>4.22</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3563,7 +3960,7 @@
       <c r="C20" s="8" t="n">
         <v>14.39</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3579,7 +3976,7 @@
       <c r="C21" s="8" t="n">
         <v>8.69</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3595,7 +3992,7 @@
       <c r="C22" s="8" t="n">
         <v>13.17</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3611,7 +4008,7 @@
       <c r="C23" s="8" t="n">
         <v>6.05</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3627,14 +4024,13 @@
       <c r="C24" s="8" t="n">
         <v>7.87</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3652,25 +4048,31 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 4 — Максимальный сток (годовые максимумы)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Q_max, м³/с</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -3683,6 +4085,7 @@
       <c r="B4" s="8" t="n">
         <v>349.9</v>
       </c>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -3691,6 +4094,7 @@
       <c r="B5" s="8" t="n">
         <v>748.8</v>
       </c>
+      <c r="C5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -3699,6 +4103,7 @@
       <c r="B6" s="8" t="n">
         <v>567.4</v>
       </c>
+      <c r="C6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -3707,6 +4112,7 @@
       <c r="B7" s="8" t="n">
         <v>390.3</v>
       </c>
+      <c r="C7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -3715,6 +4121,7 @@
       <c r="B8" s="8" t="n">
         <v>317.7</v>
       </c>
+      <c r="C8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -3723,6 +4130,7 @@
       <c r="B9" s="8" t="n">
         <v>798.7</v>
       </c>
+      <c r="C9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -3731,6 +4139,7 @@
       <c r="B10" s="8" t="n">
         <v>473.3</v>
       </c>
+      <c r="C10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -3739,6 +4148,7 @@
       <c r="B11" s="8" t="n">
         <v>653.1</v>
       </c>
+      <c r="C11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -3747,6 +4157,7 @@
       <c r="B12" s="8" t="n">
         <v>442.9</v>
       </c>
+      <c r="C12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -3755,6 +4166,7 @@
       <c r="B13" s="8" t="n">
         <v>325.7</v>
       </c>
+      <c r="C13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -3763,6 +4175,7 @@
       <c r="B14" s="8" t="n">
         <v>852.4</v>
       </c>
+      <c r="C14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -3771,6 +4184,7 @@
       <c r="B15" s="8" t="n">
         <v>528.4</v>
       </c>
+      <c r="C15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -3779,6 +4193,7 @@
       <c r="B16" s="8" t="n">
         <v>376.5</v>
       </c>
+      <c r="C16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -3787,6 +4202,7 @@
       <c r="B17" s="8" t="n">
         <v>891.7</v>
       </c>
+      <c r="C17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -3795,6 +4211,7 @@
       <c r="B18" s="8" t="n">
         <v>602.9</v>
       </c>
+      <c r="C18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -3803,6 +4220,7 @@
       <c r="B19" s="8" t="n">
         <v>500.7</v>
       </c>
+      <c r="C19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -3811,6 +4229,7 @@
       <c r="B20" s="8" t="n">
         <v>457.6</v>
       </c>
+      <c r="C20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -3819,6 +4238,7 @@
       <c r="B21" s="8" t="n">
         <v>794.7</v>
       </c>
+      <c r="C21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -3827,6 +4247,7 @@
       <c r="B22" s="8" t="n">
         <v>434.4</v>
       </c>
+      <c r="C22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -3835,6 +4256,7 @@
       <c r="B23" s="8" t="n">
         <v>429.4</v>
       </c>
+      <c r="C23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -3843,9 +4265,9 @@
       <c r="B24" s="8" t="n">
         <v>802.6</v>
       </c>
+      <c r="C24" s="11" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -3863,20 +4285,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 4 — Кривая расходов Q=f(H)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>H, м</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Q, м³/с</t>
         </is>
@@ -4043,7 +4469,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -4061,32 +4486,40 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 5 — Ледовые явления</t>
         </is>
       </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Год | Дата ледостава | Дата вскрытия</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Дата ледостава</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Дата вскрытия</t>
         </is>
@@ -4408,7 +4841,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -4427,30 +4859,38 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 6 — Водный баланс</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Осадки, мм</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Сток, мм</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Испарение, мм</t>
         </is>
@@ -4737,7 +5177,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -4759,15 +5198,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Работа 7 — Ливневый сток (параметры расчёта)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="11" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Площадь бассейна F, км²:</t>
         </is>
@@ -4777,7 +5220,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Климатическая зона (zone_1 ... zone_7):</t>
         </is>
@@ -4789,7 +5232,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Обеспеченность T, лет:</t>
         </is>
@@ -4799,7 +5242,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Время концентрации t, мин:</t>
         </is>
@@ -4809,7 +5252,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Коэфф. стока α:</t>
         </is>
@@ -4819,7 +5262,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8C16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
